--- a/research/traditional_assets/database/data/latvia/latvia_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/latvia/latvia_investments_asset_management.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.01442307692307692</v>
+        <v>-0.4385382059800665</v>
       </c>
       <c r="H2">
-        <v>0.01442307692307692</v>
+        <v>-0.4385382059800665</v>
       </c>
       <c r="I2">
-        <v>-0.4355769230769231</v>
+        <v>-0.8936877076411961</v>
       </c>
       <c r="J2">
-        <v>-0.4355769230769231</v>
+        <v>-0.8936877076411961</v>
       </c>
       <c r="K2">
-        <v>-0.909</v>
+        <v>-2.67</v>
       </c>
       <c r="L2">
-        <v>-0.4370192307692308</v>
+        <v>-0.8870431893687708</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,58 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7.36</v>
+        <v>4.07</v>
       </c>
       <c r="V2">
-        <v>0.1330922242314647</v>
+        <v>0.07737642585551331</v>
+      </c>
+      <c r="W2">
+        <v>-0.3268053855569155</v>
       </c>
       <c r="X2">
-        <v>0.0842685570964543</v>
+        <v>0.07129928300612057</v>
+      </c>
+      <c r="Y2">
+        <v>-0.3981046685630361</v>
+      </c>
+      <c r="Z2">
+        <v>3.455797933409875</v>
+      </c>
+      <c r="AA2">
+        <v>-3.088404133180254</v>
       </c>
       <c r="AB2">
-        <v>0.08424046644473124</v>
+        <v>0.07127006612988793</v>
+      </c>
+      <c r="AC2">
+        <v>-3.159674199310142</v>
       </c>
       <c r="AD2">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="AG2">
-        <v>-7.299</v>
+        <v>-4.008</v>
       </c>
       <c r="AH2">
-        <v>0.001101858709199617</v>
+        <v>0.001177319509323611</v>
       </c>
       <c r="AI2">
-        <v>0.007411007168023326</v>
+        <v>0.008841985168282943</v>
       </c>
       <c r="AJ2">
-        <v>-0.152059332097248</v>
+        <v>-0.08248271320381956</v>
       </c>
       <c r="AK2">
-        <v>-8.38002296211252</v>
+        <v>-1.362338545207342</v>
       </c>
       <c r="AL2">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AM2">
-        <v>0.003</v>
+        <v>-0.034</v>
       </c>
       <c r="AN2">
-        <v>-0.06955530216647662</v>
+        <v>-0.02357414448669201</v>
       </c>
       <c r="AO2">
-        <v>-302</v>
+        <v>-1345</v>
       </c>
       <c r="AP2">
-        <v>8.322690992018245</v>
+        <v>1.523954372623574</v>
       </c>
       <c r="AQ2">
-        <v>-302</v>
+        <v>79.11764705882354</v>
       </c>
     </row>
     <row r="3">
@@ -698,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.01442307692307692</v>
+        <v>-0.4385382059800665</v>
       </c>
       <c r="H3">
-        <v>0.01442307692307692</v>
+        <v>-0.4385382059800665</v>
       </c>
       <c r="I3">
-        <v>-0.4355769230769231</v>
+        <v>-0.8936877076411961</v>
       </c>
       <c r="J3">
-        <v>-0.4355769230769231</v>
+        <v>-0.8936877076411961</v>
       </c>
       <c r="K3">
-        <v>-0.909</v>
+        <v>-2.67</v>
       </c>
       <c r="L3">
-        <v>-0.4370192307692308</v>
+        <v>-0.8870431893687708</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,58 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7.36</v>
+        <v>4.07</v>
       </c>
       <c r="V3">
-        <v>0.1330922242314647</v>
+        <v>0.07737642585551331</v>
+      </c>
+      <c r="W3">
+        <v>-0.3268053855569155</v>
       </c>
       <c r="X3">
-        <v>0.0842685570964543</v>
+        <v>0.07129928300612057</v>
+      </c>
+      <c r="Y3">
+        <v>-0.3981046685630361</v>
+      </c>
+      <c r="Z3">
+        <v>3.455797933409875</v>
+      </c>
+      <c r="AA3">
+        <v>-3.088404133180254</v>
       </c>
       <c r="AB3">
-        <v>0.08424046644473124</v>
+        <v>0.07127006612988793</v>
+      </c>
+      <c r="AC3">
+        <v>-3.159674199310142</v>
       </c>
       <c r="AD3">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.061</v>
+        <v>0.062</v>
       </c>
       <c r="AG3">
-        <v>-7.299</v>
+        <v>-4.008</v>
       </c>
       <c r="AH3">
-        <v>0.001101858709199617</v>
+        <v>0.001177319509323611</v>
       </c>
       <c r="AI3">
-        <v>0.007411007168023326</v>
+        <v>0.008841985168282943</v>
       </c>
       <c r="AJ3">
-        <v>-0.152059332097248</v>
+        <v>-0.08248271320381956</v>
       </c>
       <c r="AK3">
-        <v>-8.38002296211252</v>
+        <v>-1.362338545207342</v>
       </c>
       <c r="AL3">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AM3">
-        <v>0.003</v>
+        <v>-0.034</v>
       </c>
       <c r="AN3">
-        <v>-0.06955530216647662</v>
+        <v>-0.02357414448669201</v>
       </c>
       <c r="AO3">
-        <v>-302</v>
+        <v>-1345</v>
       </c>
       <c r="AP3">
-        <v>8.322690992018245</v>
+        <v>1.523954372623574</v>
       </c>
       <c r="AQ3">
-        <v>-302</v>
+        <v>79.11764705882354</v>
       </c>
     </row>
   </sheetData>
